--- a/docs/iap-management/templates/item-iap-template.xlsx
+++ b/docs/iap-management/templates/item-iap-template.xlsx
@@ -1,302 +1,321 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lap15063-local/Documents/DEV/appstore-connect-cpps/docs/iap-management/templates/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA70D7DA-A5B1-A343-96C1-ED9AC010C623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="90">
-  <si>
-    <t xml:space="preserve">Product ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price (USD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GT Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GT Currency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Arabic)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Arabic)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Catalan)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Catalan)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Chinese (Simplified))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Chinese (Simplified))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Chinese (Traditional))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Chinese (Traditional))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Croatian)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Croatian)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Czech)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Czech)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Danish)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Danish)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Dutch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Dutch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (English (Australia))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (English (Australia))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (English (Canada))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (English (Canada))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (English (U.K.))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (English (U.K.))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (English (U.S.))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (English (U.S.))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Finnish)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Finnish)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (French)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (French)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (French (Canada))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (French (Canada))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (German)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (German)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Greek)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Greek)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Hebrew)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Hebrew)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Hindi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Hindi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Hungarian)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Hungarian)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Indonesian)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Indonesian)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Italian)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Italian)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Japanese)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Japanese)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Korean)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Korean)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Malay)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Malay)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Norwegian)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Norwegian)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Polish)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Polish)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Portuguese (Brazil))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Portuguese (Brazil))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Portuguese (Portugal))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Portuguese (Portugal))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Romanian)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Romanian)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Russian)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Russian)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Slovak)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Slovak)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Spanish (Mexico))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Spanish (Mexico))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Spanish (Spain))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Spanish (Spain))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Swedish)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Swedish)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Thai)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Thai)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Turkish)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Turkish)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Ukrainian)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Ukrainian)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display Name (Vietnamese)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (Vietnamese)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">com.vng.example.product1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Example 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">com.vng.example.product2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Example 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">com.vng.example.product3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Example 3</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="91">
+  <si>
+    <t>Product ID</t>
+  </si>
+  <si>
+    <t>Reference Name</t>
+  </si>
+  <si>
+    <t>Price (USD)</t>
+  </si>
+  <si>
+    <t>GT Price</t>
+  </si>
+  <si>
+    <t>GT Currency</t>
+  </si>
+  <si>
+    <t>Display Name (Arabic)</t>
+  </si>
+  <si>
+    <t>Description (Arabic)</t>
+  </si>
+  <si>
+    <t>Display Name (Catalan)</t>
+  </si>
+  <si>
+    <t>Description (Catalan)</t>
+  </si>
+  <si>
+    <t>Display Name (Chinese (Simplified))</t>
+  </si>
+  <si>
+    <t>Description (Chinese (Simplified))</t>
+  </si>
+  <si>
+    <t>Display Name (Chinese (Traditional))</t>
+  </si>
+  <si>
+    <t>Description (Chinese (Traditional))</t>
+  </si>
+  <si>
+    <t>Display Name (Croatian)</t>
+  </si>
+  <si>
+    <t>Description (Croatian)</t>
+  </si>
+  <si>
+    <t>Display Name (Czech)</t>
+  </si>
+  <si>
+    <t>Description (Czech)</t>
+  </si>
+  <si>
+    <t>Display Name (Danish)</t>
+  </si>
+  <si>
+    <t>Description (Danish)</t>
+  </si>
+  <si>
+    <t>Display Name (Dutch)</t>
+  </si>
+  <si>
+    <t>Description (Dutch)</t>
+  </si>
+  <si>
+    <t>Display Name (English (Australia))</t>
+  </si>
+  <si>
+    <t>Description (English (Australia))</t>
+  </si>
+  <si>
+    <t>Display Name (English (Canada))</t>
+  </si>
+  <si>
+    <t>Description (English (Canada))</t>
+  </si>
+  <si>
+    <t>Display Name (English (U.K.))</t>
+  </si>
+  <si>
+    <t>Description (English (U.K.))</t>
+  </si>
+  <si>
+    <t>Display Name (English (U.S.))</t>
+  </si>
+  <si>
+    <t>Description (English (U.S.))</t>
+  </si>
+  <si>
+    <t>Display Name (Finnish)</t>
+  </si>
+  <si>
+    <t>Description (Finnish)</t>
+  </si>
+  <si>
+    <t>Display Name (French)</t>
+  </si>
+  <si>
+    <t>Description (French)</t>
+  </si>
+  <si>
+    <t>Display Name (French (Canada))</t>
+  </si>
+  <si>
+    <t>Description (French (Canada))</t>
+  </si>
+  <si>
+    <t>Display Name (German)</t>
+  </si>
+  <si>
+    <t>Description (German)</t>
+  </si>
+  <si>
+    <t>Display Name (Greek)</t>
+  </si>
+  <si>
+    <t>Description (Greek)</t>
+  </si>
+  <si>
+    <t>Display Name (Hebrew)</t>
+  </si>
+  <si>
+    <t>Description (Hebrew)</t>
+  </si>
+  <si>
+    <t>Display Name (Hindi)</t>
+  </si>
+  <si>
+    <t>Description (Hindi)</t>
+  </si>
+  <si>
+    <t>Display Name (Hungarian)</t>
+  </si>
+  <si>
+    <t>Description (Hungarian)</t>
+  </si>
+  <si>
+    <t>Display Name (Indonesian)</t>
+  </si>
+  <si>
+    <t>Description (Indonesian)</t>
+  </si>
+  <si>
+    <t>Display Name (Italian)</t>
+  </si>
+  <si>
+    <t>Description (Italian)</t>
+  </si>
+  <si>
+    <t>Display Name (Japanese)</t>
+  </si>
+  <si>
+    <t>Description (Japanese)</t>
+  </si>
+  <si>
+    <t>Display Name (Korean)</t>
+  </si>
+  <si>
+    <t>Description (Korean)</t>
+  </si>
+  <si>
+    <t>Display Name (Malay)</t>
+  </si>
+  <si>
+    <t>Description (Malay)</t>
+  </si>
+  <si>
+    <t>Display Name (Norwegian)</t>
+  </si>
+  <si>
+    <t>Description (Norwegian)</t>
+  </si>
+  <si>
+    <t>Display Name (Polish)</t>
+  </si>
+  <si>
+    <t>Description (Polish)</t>
+  </si>
+  <si>
+    <t>Display Name (Portuguese (Brazil))</t>
+  </si>
+  <si>
+    <t>Description (Portuguese (Brazil))</t>
+  </si>
+  <si>
+    <t>Display Name (Portuguese (Portugal))</t>
+  </si>
+  <si>
+    <t>Description (Portuguese (Portugal))</t>
+  </si>
+  <si>
+    <t>Display Name (Romanian)</t>
+  </si>
+  <si>
+    <t>Description (Romanian)</t>
+  </si>
+  <si>
+    <t>Display Name (Russian)</t>
+  </si>
+  <si>
+    <t>Description (Russian)</t>
+  </si>
+  <si>
+    <t>Display Name (Slovak)</t>
+  </si>
+  <si>
+    <t>Description (Slovak)</t>
+  </si>
+  <si>
+    <t>Display Name (Spanish (Mexico))</t>
+  </si>
+  <si>
+    <t>Description (Spanish (Mexico))</t>
+  </si>
+  <si>
+    <t>Display Name (Spanish (Spain))</t>
+  </si>
+  <si>
+    <t>Description (Spanish (Spain))</t>
+  </si>
+  <si>
+    <t>Display Name (Swedish)</t>
+  </si>
+  <si>
+    <t>Description (Swedish)</t>
+  </si>
+  <si>
+    <t>Display Name (Thai)</t>
+  </si>
+  <si>
+    <t>Description (Thai)</t>
+  </si>
+  <si>
+    <t>Display Name (Turkish)</t>
+  </si>
+  <si>
+    <t>Description (Turkish)</t>
+  </si>
+  <si>
+    <t>Display Name (Ukrainian)</t>
+  </si>
+  <si>
+    <t>Description (Ukrainian)</t>
+  </si>
+  <si>
+    <t>Display Name (Vietnamese)</t>
+  </si>
+  <si>
+    <t>Description (Vietnamese)</t>
+  </si>
+  <si>
+    <t>com.vng.example.product1</t>
+  </si>
+  <si>
+    <t>Example 1</t>
+  </si>
+  <si>
+    <t>VND</t>
+  </si>
+  <si>
+    <t>com.vng.example.product2</t>
+  </si>
+  <si>
+    <t>Example 2</t>
+  </si>
+  <si>
+    <t>com.vng.example.product3</t>
+  </si>
+  <si>
+    <t>Example 3</t>
+  </si>
+  <si>
+    <t>Type</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
-    <font/>
     <font>
-      <color rgb="FFff0000"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -304,37 +323,46 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -524,17 +552,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr defaultRowHeight="15.75" defaultColWidth="14.43"/>
+  <dimension ref="A1:FA4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:157" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -542,249 +573,251 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="CF1" s="2"/>
       <c r="CG1" s="2"/>
       <c r="CH1" s="2"/>
       <c r="CI1" s="2"/>
@@ -857,59 +890,63 @@
       <c r="EX1" s="2"/>
       <c r="EY1" s="2"/>
       <c r="EZ1" s="2"/>
+      <c r="FA1" s="2"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:157" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="1"/>
+      <c r="D2" s="3">
         <v>0.99</v>
       </c>
-      <c r="D2" s="4">
+      <c r="E2" s="4">
         <v>23000</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:157" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="1"/>
+      <c r="D3" s="3">
         <v>0.99</v>
       </c>
-      <c r="D3" s="4">
+      <c r="E3" s="4">
         <v>23000</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:157" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>88</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="1"/>
+      <c r="D4" s="3">
         <v>0.99</v>
       </c>
-      <c r="D4" s="4">
+      <c r="E4" s="4">
         <v>23000</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>